--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/61.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/3_fold/61.xlsx
@@ -426,13 +426,13 @@
         <v>-2.286429439109674</v>
       </c>
       <c r="E2">
-        <v>-16.11984344827349</v>
+        <v>-29.93829168677126</v>
       </c>
       <c r="F2">
-        <v>-6.226075972691638</v>
+        <v>-6.188341011844463</v>
       </c>
       <c r="G2">
-        <v>-6.531134775272092</v>
+        <v>-16.68216124597316</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-2.310085865381021</v>
       </c>
       <c r="E3">
-        <v>-17.8370498489301</v>
+        <v>-29.34726243013417</v>
       </c>
       <c r="F3">
-        <v>-6.016761521112795</v>
+        <v>-6.940150757345258</v>
       </c>
       <c r="G3">
-        <v>-7.15336174101473</v>
+        <v>-15.57112726553882</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-2.388628068184294</v>
       </c>
       <c r="E4">
-        <v>-18.38702396021365</v>
+        <v>-29.33429288057621</v>
       </c>
       <c r="F4">
-        <v>-5.803121176825929</v>
+        <v>-6.624389492292546</v>
       </c>
       <c r="G4">
-        <v>-5.384461116834731</v>
+        <v>-16.89085638149604</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-2.49974549810914</v>
       </c>
       <c r="E5">
-        <v>-18.51489448076824</v>
+        <v>-29.44127807900742</v>
       </c>
       <c r="F5">
-        <v>-6.074532737349153</v>
+        <v>-6.591036249786913</v>
       </c>
       <c r="G5">
-        <v>-6.128943218797114</v>
+        <v>-15.61911527840332</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-2.625674261917619</v>
       </c>
       <c r="E6">
-        <v>-18.72708518734565</v>
+        <v>-31.05458317203204</v>
       </c>
       <c r="F6">
-        <v>-6.131270981402166</v>
+        <v>-7.013432393390951</v>
       </c>
       <c r="G6">
-        <v>-5.598173384122383</v>
+        <v>-16.70059436353582</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-2.746343473596247</v>
       </c>
       <c r="E7">
-        <v>-19.27250818225149</v>
+        <v>-31.21746332513993</v>
       </c>
       <c r="F7">
-        <v>-6.15728612254861</v>
+        <v>-6.8279634058544</v>
       </c>
       <c r="G7">
-        <v>-5.668141764094879</v>
+        <v>-16.1105127949795</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-2.84285473366574</v>
       </c>
       <c r="E8">
-        <v>-19.03102730579247</v>
+        <v>-30.78043388408169</v>
       </c>
       <c r="F8">
-        <v>-6.451008536082067</v>
+        <v>-6.758418523916187</v>
       </c>
       <c r="G8">
-        <v>-6.354629729300309</v>
+        <v>-14.74320782907741</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-2.893365515590851</v>
       </c>
       <c r="E9">
-        <v>-19.70780774623881</v>
+        <v>-32.00318526478879</v>
       </c>
       <c r="F9">
-        <v>-6.129877320196579</v>
+        <v>-6.984763752983187</v>
       </c>
       <c r="G9">
-        <v>-5.140619574594172</v>
+        <v>-15.11705283937238</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-2.880635968094154</v>
       </c>
       <c r="E10">
-        <v>-21.32465410593743</v>
+        <v>-32.78343680783639</v>
       </c>
       <c r="F10">
-        <v>-6.196982899098537</v>
+        <v>-6.395871022783084</v>
       </c>
       <c r="G10">
-        <v>-5.645709507520777</v>
+        <v>-15.80646567156176</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-2.791220438948907</v>
       </c>
       <c r="E11">
-        <v>-21.38988224554391</v>
+        <v>-33.47363511676745</v>
       </c>
       <c r="F11">
-        <v>-5.90666070216553</v>
+        <v>-6.339048446390075</v>
       </c>
       <c r="G11">
-        <v>-5.20004386702409</v>
+        <v>-15.05168280715393</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-2.616139389548325</v>
       </c>
       <c r="E12">
-        <v>-21.92699549064568</v>
+        <v>-32.59682745092831</v>
       </c>
       <c r="F12">
-        <v>-5.879851728428971</v>
+        <v>-6.087161208318867</v>
       </c>
       <c r="G12">
-        <v>-4.995121098143204</v>
+        <v>-14.57284384508098</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-2.353662770157242</v>
       </c>
       <c r="E13">
-        <v>-22.19853637756762</v>
+        <v>-34.17035669250656</v>
       </c>
       <c r="F13">
-        <v>-5.820575199719988</v>
+        <v>-6.396024246330404</v>
       </c>
       <c r="G13">
-        <v>-4.194793403478855</v>
+        <v>-13.61957225704784</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-2.011664642731594</v>
       </c>
       <c r="E14">
-        <v>-23.38025072681721</v>
+        <v>-33.08233420623866</v>
       </c>
       <c r="F14">
-        <v>-6.010563688012723</v>
+        <v>-6.42431675658325</v>
       </c>
       <c r="G14">
-        <v>-3.457183994055999</v>
+        <v>-15.12256986351358</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-1.602465117279464</v>
       </c>
       <c r="E15">
-        <v>-24.51290811714172</v>
+        <v>-34.37133716167799</v>
       </c>
       <c r="F15">
-        <v>-5.876717574422316</v>
+        <v>-6.371372280050673</v>
       </c>
       <c r="G15">
-        <v>-4.041203953729908</v>
+        <v>-13.90379252323089</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-1.143690978629765</v>
       </c>
       <c r="E16">
-        <v>-25.00839562916498</v>
+        <v>-34.34618375280238</v>
       </c>
       <c r="F16">
-        <v>-6.059179500351926</v>
+        <v>-6.581768006843283</v>
       </c>
       <c r="G16">
-        <v>-4.14203323921949</v>
+        <v>-14.41924777424095</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-0.6589846122797945</v>
       </c>
       <c r="E17">
-        <v>-25.25616202754664</v>
+        <v>-34.19166995542366</v>
       </c>
       <c r="F17">
-        <v>-5.589948025784118</v>
+        <v>-5.816897834584337</v>
       </c>
       <c r="G17">
-        <v>-3.269922985627124</v>
+        <v>-13.36488867816617</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-0.1710060728561303</v>
       </c>
       <c r="E18">
-        <v>-25.29022068055833</v>
+        <v>-35.61739433386556</v>
       </c>
       <c r="F18">
-        <v>-5.800309306973067</v>
+        <v>-5.934589355984304</v>
       </c>
       <c r="G18">
-        <v>-2.707064033040237</v>
+        <v>-14.90055474801343</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>0.2987569280503202</v>
       </c>
       <c r="E19">
-        <v>-26.80542091268079</v>
+        <v>-36.56178268155817</v>
       </c>
       <c r="F19">
-        <v>-4.987964778413472</v>
+        <v>-5.755616334186407</v>
       </c>
       <c r="G19">
-        <v>-2.469740954966503</v>
+        <v>-13.7026040497183</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>0.7295256931743673</v>
       </c>
       <c r="E20">
-        <v>-28.18333592678671</v>
+        <v>-36.95117257605573</v>
       </c>
       <c r="F20">
-        <v>-5.153908651645048</v>
+        <v>-4.850348652891361</v>
       </c>
       <c r="G20">
-        <v>-3.532108260700785</v>
+        <v>-12.49299029948832</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>1.104873577436951</v>
       </c>
       <c r="E21">
-        <v>-28.01494914928549</v>
+        <v>-37.92628661989038</v>
       </c>
       <c r="F21">
-        <v>-4.650458835215298</v>
+        <v>-5.182898388427168</v>
       </c>
       <c r="G21">
-        <v>-3.088829523537912</v>
+        <v>-13.18538096739027</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>1.414208741395536</v>
       </c>
       <c r="E22">
-        <v>-28.40181668376077</v>
+        <v>-37.88718777530816</v>
       </c>
       <c r="F22">
-        <v>-4.832862955878994</v>
+        <v>-5.101032670393313</v>
       </c>
       <c r="G22">
-        <v>-2.536286230851394</v>
+        <v>-13.28008243308666</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>1.651743709340133</v>
       </c>
       <c r="E23">
-        <v>-29.34513404735057</v>
+        <v>-37.21439692046258</v>
       </c>
       <c r="F23">
-        <v>-4.477078670857776</v>
+        <v>-4.873176981809463</v>
       </c>
       <c r="G23">
-        <v>-2.22269480464393</v>
+        <v>-12.38824794917132</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>1.813909990207867</v>
       </c>
       <c r="E24">
-        <v>-30.79321097349433</v>
+        <v>-39.40605380713982</v>
       </c>
       <c r="F24">
-        <v>-4.132115056503798</v>
+        <v>-5.389057305969497</v>
       </c>
       <c r="G24">
-        <v>-2.716525572191474</v>
+        <v>-12.46157653286617</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>1.904115280727258</v>
       </c>
       <c r="E25">
-        <v>-30.0592245851461</v>
+        <v>-39.67014535431914</v>
       </c>
       <c r="F25">
-        <v>-4.013043335398526</v>
+        <v>-5.931575563627223</v>
       </c>
       <c r="G25">
-        <v>-1.878811886752136</v>
+        <v>-12.91881915111369</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>1.929455199392377</v>
       </c>
       <c r="E26">
-        <v>-29.95642369669797</v>
+        <v>-39.07526010206452</v>
       </c>
       <c r="F26">
-        <v>-3.954686147973455</v>
+        <v>-5.315139416072276</v>
       </c>
       <c r="G26">
-        <v>-3.184924728906337</v>
+        <v>-11.73041937669936</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>1.89870507514349</v>
       </c>
       <c r="E27">
-        <v>-29.69299330672377</v>
+        <v>-38.59509694608322</v>
       </c>
       <c r="F27">
-        <v>-4.089506240701858</v>
+        <v>-5.153804127054629</v>
       </c>
       <c r="G27">
-        <v>-2.046116926670284</v>
+        <v>-11.9642531397747</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>1.825452566031695</v>
       </c>
       <c r="E28">
-        <v>-29.37300680486778</v>
+        <v>-39.40521377521139</v>
       </c>
       <c r="F28">
-        <v>-4.119600612359996</v>
+        <v>-5.155694280064706</v>
       </c>
       <c r="G28">
-        <v>-3.462047185453188</v>
+        <v>-12.34739250667117</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>1.725862843507343</v>
       </c>
       <c r="E29">
-        <v>-31.92986927060461</v>
+        <v>-37.79811495581428</v>
       </c>
       <c r="F29">
-        <v>-4.148224513075648</v>
+        <v>-5.223058794883839</v>
       </c>
       <c r="G29">
-        <v>-2.227243494214889</v>
+        <v>-12.64751332307934</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>1.614723729772189</v>
       </c>
       <c r="E30">
-        <v>-30.11924271540676</v>
+        <v>-38.28253261312579</v>
       </c>
       <c r="F30">
-        <v>-4.353124384415204</v>
+        <v>-5.235886812798898</v>
       </c>
       <c r="G30">
-        <v>-3.4193841850886</v>
+        <v>-13.2886931620343</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>1.510898055105523</v>
       </c>
       <c r="E31">
-        <v>-29.4978862683403</v>
+        <v>-38.71833257349095</v>
       </c>
       <c r="F31">
-        <v>-4.207132038306334</v>
+        <v>-5.328912114565895</v>
       </c>
       <c r="G31">
-        <v>-2.716538814373631</v>
+        <v>-12.68335328908749</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>1.43194743398774</v>
       </c>
       <c r="E32">
-        <v>-29.53819874395658</v>
+        <v>-37.10866158085748</v>
       </c>
       <c r="F32">
-        <v>-4.114731508522977</v>
+        <v>-4.495279411090964</v>
       </c>
       <c r="G32">
-        <v>-4.373533067689646</v>
+        <v>-12.82683895385058</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>1.390806344396861</v>
       </c>
       <c r="E33">
-        <v>-29.77506284116479</v>
+        <v>-37.98025018040278</v>
       </c>
       <c r="F33">
-        <v>-4.182383465965762</v>
+        <v>-5.883188596792801</v>
       </c>
       <c r="G33">
-        <v>-3.313075946731524</v>
+        <v>-12.74155267966788</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>1.399679457375088</v>
       </c>
       <c r="E34">
-        <v>-28.76087033088094</v>
+        <v>-36.31574842448444</v>
       </c>
       <c r="F34">
-        <v>-4.141135845398141</v>
+        <v>-5.26679916856236</v>
       </c>
       <c r="G34">
-        <v>-3.246239342839178</v>
+        <v>-12.991469072973</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>1.468441637978575</v>
       </c>
       <c r="E35">
-        <v>-28.45191066323362</v>
+        <v>-36.81800374091216</v>
       </c>
       <c r="F35">
-        <v>-4.395143269763643</v>
+        <v>-5.033506617570806</v>
       </c>
       <c r="G35">
-        <v>-4.476590350327157</v>
+        <v>-14.72896751744024</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>1.599715513075349</v>
       </c>
       <c r="E36">
-        <v>-27.84895793453434</v>
+        <v>-37.486225365484</v>
       </c>
       <c r="F36">
-        <v>-3.896898302824985</v>
+        <v>-5.39095221009732</v>
       </c>
       <c r="G36">
-        <v>-3.88021212415515</v>
+        <v>-13.02881533720151</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>1.790426078692344</v>
       </c>
       <c r="E37">
-        <v>-27.37849024140345</v>
+        <v>-37.64906023385181</v>
       </c>
       <c r="F37">
-        <v>-4.168399342732431</v>
+        <v>-4.979081771933772</v>
       </c>
       <c r="G37">
-        <v>-2.550786420313401</v>
+        <v>-13.10199163580157</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>2.038789931322295</v>
       </c>
       <c r="E38">
-        <v>-26.54848888290759</v>
+        <v>-36.0603243765558</v>
       </c>
       <c r="F38">
-        <v>-4.279372783639104</v>
+        <v>-4.969889150947604</v>
       </c>
       <c r="G38">
-        <v>-2.678166281027939</v>
+        <v>-13.48631121218279</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>2.33659171971564</v>
       </c>
       <c r="E39">
-        <v>-25.7542443551763</v>
+        <v>-36.97545425368485</v>
       </c>
       <c r="F39">
-        <v>-4.032705836191663</v>
+        <v>-4.706304265058481</v>
       </c>
       <c r="G39">
-        <v>-2.294368115569152</v>
+        <v>-13.93053345482435</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>2.667775013752725</v>
       </c>
       <c r="E40">
-        <v>-26.06659132138135</v>
+        <v>-36.28216752548056</v>
       </c>
       <c r="F40">
-        <v>-4.079658757319654</v>
+        <v>-4.815139702979311</v>
       </c>
       <c r="G40">
-        <v>-2.893076965800807</v>
+        <v>-13.41875125409011</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>3.020390945972363</v>
       </c>
       <c r="E41">
-        <v>-25.25183280639531</v>
+        <v>-35.35198500075001</v>
       </c>
       <c r="F41">
-        <v>-4.340254398293385</v>
+        <v>-4.349684575166869</v>
       </c>
       <c r="G41">
-        <v>-3.609310182676588</v>
+        <v>-14.28358989440547</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>3.378977121198767</v>
       </c>
       <c r="E42">
-        <v>-25.20806510511117</v>
+        <v>-34.59251688916062</v>
       </c>
       <c r="F42">
-        <v>-4.020222274313213</v>
+        <v>-4.533613804627134</v>
       </c>
       <c r="G42">
-        <v>-1.996912288320096</v>
+        <v>-13.13538179811065</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>3.724856564871775</v>
       </c>
       <c r="E43">
-        <v>-24.56577805118127</v>
+        <v>-36.27540651378711</v>
       </c>
       <c r="F43">
-        <v>-3.655823420964961</v>
+        <v>-4.056340271420725</v>
       </c>
       <c r="G43">
-        <v>-2.843061243793497</v>
+        <v>-13.64720538066414</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>4.041884003959066</v>
       </c>
       <c r="E44">
-        <v>-23.22794003204323</v>
+        <v>-35.85974467733406</v>
       </c>
       <c r="F44">
-        <v>-3.7262555741423</v>
+        <v>-5.010298991085957</v>
       </c>
       <c r="G44">
-        <v>-3.485168035499458</v>
+        <v>-13.94788898981398</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>4.31804173839054</v>
       </c>
       <c r="E45">
-        <v>-23.08502592083516</v>
+        <v>-34.85783565279602</v>
       </c>
       <c r="F45">
-        <v>-4.243568360302849</v>
+        <v>-4.614925225590583</v>
       </c>
       <c r="G45">
-        <v>-4.517452413918382</v>
+        <v>-14.43309247568618</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>4.54132010483713</v>
       </c>
       <c r="E46">
-        <v>-22.87187064929412</v>
+        <v>-34.17392739426161</v>
       </c>
       <c r="F46">
-        <v>-3.766237813683484</v>
+        <v>-4.757462717244922</v>
       </c>
       <c r="G46">
-        <v>-2.755868095380173</v>
+        <v>-13.14917022028172</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>4.70075361438573</v>
       </c>
       <c r="E47">
-        <v>-21.8258746660544</v>
+        <v>-33.97731916674459</v>
       </c>
       <c r="F47">
-        <v>-3.949543063013065</v>
+        <v>-4.741906765890518</v>
       </c>
       <c r="G47">
-        <v>-3.978445941941944</v>
+        <v>-14.36721924054577</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>4.793778831084032</v>
       </c>
       <c r="E48">
-        <v>-22.50650430940725</v>
+        <v>-34.54047340162747</v>
       </c>
       <c r="F48">
-        <v>-3.723614744528304</v>
+        <v>-4.227889671739998</v>
       </c>
       <c r="G48">
-        <v>-2.956987047436437</v>
+        <v>-14.32972731231352</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>4.818434820396632</v>
       </c>
       <c r="E49">
-        <v>-21.42369636095919</v>
+        <v>-33.32298184348027</v>
       </c>
       <c r="F49">
-        <v>-3.957411705853926</v>
+        <v>-4.486153305753244</v>
       </c>
       <c r="G49">
-        <v>-3.088846076265608</v>
+        <v>-13.84956247675209</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>4.773106925043205</v>
       </c>
       <c r="E50">
-        <v>-21.41546359521324</v>
+        <v>-33.12835482334161</v>
       </c>
       <c r="F50">
-        <v>-3.545993415729236</v>
+        <v>-4.535817531408467</v>
       </c>
       <c r="G50">
-        <v>-4.716489032830444</v>
+        <v>-12.96538528466908</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>4.66431121920279</v>
       </c>
       <c r="E51">
-        <v>-21.12100410133849</v>
+        <v>-31.66862386933911</v>
       </c>
       <c r="F51">
-        <v>-3.535783263692398</v>
+        <v>-4.456423186455657</v>
       </c>
       <c r="G51">
-        <v>-4.516515529530769</v>
+        <v>-13.73234268029757</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>4.499268194205964</v>
       </c>
       <c r="E52">
-        <v>-20.85540457231461</v>
+        <v>-31.31419379418077</v>
       </c>
       <c r="F52">
-        <v>-3.575752833586258</v>
+        <v>-4.521688499083874</v>
       </c>
       <c r="G52">
-        <v>-4.406330642347205</v>
+        <v>-13.73426610725589</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>4.284277014871102</v>
       </c>
       <c r="E53">
-        <v>-19.379076761074</v>
+        <v>-30.4309307886437</v>
       </c>
       <c r="F53">
-        <v>-3.967091316409092</v>
+        <v>-5.055573975796539</v>
       </c>
       <c r="G53">
-        <v>-4.162853260115966</v>
+        <v>-13.95801263807307</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>4.02928076126594</v>
       </c>
       <c r="E54">
-        <v>-20.09362920321831</v>
+        <v>-30.60504835000162</v>
       </c>
       <c r="F54">
-        <v>-3.231417158627752</v>
+        <v>-4.497119677364704</v>
       </c>
       <c r="G54">
-        <v>-4.476077215768571</v>
+        <v>-13.9526578306633</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>3.745107244204835</v>
       </c>
       <c r="E55">
-        <v>-20.01401863016347</v>
+        <v>-29.23871490817032</v>
       </c>
       <c r="F55">
-        <v>-3.679320865632336</v>
+        <v>-4.705087978915424</v>
       </c>
       <c r="G55">
-        <v>-3.858038090133111</v>
+        <v>-14.16418017207673</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>3.439315830301095</v>
       </c>
       <c r="E56">
-        <v>-17.64502443710885</v>
+        <v>-29.6603611230245</v>
       </c>
       <c r="F56">
-        <v>-3.619975445716032</v>
+        <v>-4.198893600134218</v>
       </c>
       <c r="G56">
-        <v>-5.232669293313608</v>
+        <v>-14.30246165925208</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>3.118522553054706</v>
       </c>
       <c r="E57">
-        <v>-18.07291088914561</v>
+        <v>-30.3138606785974</v>
       </c>
       <c r="F57">
-        <v>-3.455338129864693</v>
+        <v>-4.940428261655642</v>
       </c>
       <c r="G57">
-        <v>-4.201735617474707</v>
+        <v>-15.23631524242463</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>2.792193101001375</v>
       </c>
       <c r="E58">
-        <v>-17.07124413796698</v>
+        <v>-29.96103368323778</v>
       </c>
       <c r="F58">
-        <v>-3.518718832453537</v>
+        <v>-4.364477972122989</v>
       </c>
       <c r="G58">
-        <v>-5.299052352467074</v>
+        <v>-13.73169546864465</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>2.464886330342958</v>
       </c>
       <c r="E59">
-        <v>-17.60711658119064</v>
+        <v>-28.78404253237819</v>
       </c>
       <c r="F59">
-        <v>-3.738810402786946</v>
+        <v>-4.645333171019979</v>
       </c>
       <c r="G59">
-        <v>-5.229322331773405</v>
+        <v>-15.41467584917117</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>2.138117365597414</v>
       </c>
       <c r="E60">
-        <v>-16.66363619253657</v>
+        <v>-28.44402206151226</v>
       </c>
       <c r="F60">
-        <v>-3.748749741112244</v>
+        <v>-4.470611607752079</v>
       </c>
       <c r="G60">
-        <v>-5.799653185642427</v>
+        <v>-14.81404688252674</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>1.818967733110754</v>
       </c>
       <c r="E61">
-        <v>-16.84246110262546</v>
+        <v>-31.30182426742882</v>
       </c>
       <c r="F61">
-        <v>-3.81032739451636</v>
+        <v>-4.69358473099863</v>
       </c>
       <c r="G61">
-        <v>-5.260368627840689</v>
+        <v>-14.62627273953928</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>1.510632633269744</v>
       </c>
       <c r="E62">
-        <v>-16.8543483468956</v>
+        <v>-28.31532735868828</v>
       </c>
       <c r="F62">
-        <v>-3.645011460680256</v>
+        <v>-4.663844317612592</v>
       </c>
       <c r="G62">
-        <v>-5.92623189433646</v>
+        <v>-15.27868525950899</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>1.214793919499246</v>
       </c>
       <c r="E63">
-        <v>-16.19532405303334</v>
+        <v>-26.62823531018267</v>
       </c>
       <c r="F63">
-        <v>-3.900683359962885</v>
+        <v>-5.613185742681361</v>
       </c>
       <c r="G63">
-        <v>-5.597157046641827</v>
+        <v>-15.70948655053435</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>0.9366890597186077</v>
       </c>
       <c r="E64">
-        <v>-16.27895138253299</v>
+        <v>-30.14611468016827</v>
       </c>
       <c r="F64">
-        <v>-4.001964520667069</v>
+        <v>-4.614041517689768</v>
       </c>
       <c r="G64">
-        <v>-5.266705012002855</v>
+        <v>-14.81714224260596</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>0.6820476530952015</v>
       </c>
       <c r="E65">
-        <v>-15.5437490989137</v>
+        <v>-29.08376864152387</v>
       </c>
       <c r="F65">
-        <v>-3.943324641736092</v>
+        <v>-4.965148327289736</v>
       </c>
       <c r="G65">
-        <v>-5.498247877565021</v>
+        <v>-15.54999108754334</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>0.4549817605494321</v>
       </c>
       <c r="E66">
-        <v>-15.02785175453787</v>
+        <v>-29.60712664682733</v>
       </c>
       <c r="F66">
-        <v>-3.470517159211223</v>
+        <v>-5.086888592862524</v>
       </c>
       <c r="G66">
-        <v>-6.298883452964522</v>
+        <v>-15.59564019998435</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>0.2592133997161866</v>
       </c>
       <c r="E67">
-        <v>-15.52340719367124</v>
+        <v>-28.49914717560763</v>
       </c>
       <c r="F67">
-        <v>-4.107589786697303</v>
+        <v>-5.373864815122687</v>
       </c>
       <c r="G67">
-        <v>-6.26037187670618</v>
+        <v>-15.22666169163211</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>0.1025042546893508</v>
       </c>
       <c r="E68">
-        <v>-16.39209077714062</v>
+        <v>-29.30334528920779</v>
       </c>
       <c r="F68">
-        <v>-3.798417134179298</v>
+        <v>-4.781653033250302</v>
       </c>
       <c r="G68">
-        <v>-5.787619352607176</v>
+        <v>-14.69001563862517</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-0.01038738366241426</v>
       </c>
       <c r="E69">
-        <v>-14.59598024537436</v>
+        <v>-29.08893563036662</v>
       </c>
       <c r="F69">
-        <v>-3.648309528249159</v>
+        <v>-4.989503348710321</v>
       </c>
       <c r="G69">
-        <v>-6.462527029516236</v>
+        <v>-15.5632564435192</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-0.07674414721526894</v>
       </c>
       <c r="E70">
-        <v>-16.46481806970381</v>
+        <v>-28.0183772041093</v>
       </c>
       <c r="F70">
-        <v>-3.935030773856936</v>
+        <v>-5.436532850049583</v>
       </c>
       <c r="G70">
-        <v>-5.567607117158292</v>
+        <v>-15.84875458028041</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-0.09233781560514298</v>
       </c>
       <c r="E71">
-        <v>-16.03812713480508</v>
+        <v>-27.52497731860358</v>
       </c>
       <c r="F71">
-        <v>-3.774682925477565</v>
+        <v>-5.862616256951243</v>
       </c>
       <c r="G71">
-        <v>-5.834774763268555</v>
+        <v>-14.864185094719</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-0.05473617476012228</v>
       </c>
       <c r="E72">
-        <v>-16.09371415324923</v>
+        <v>-29.31065424625617</v>
       </c>
       <c r="F72">
-        <v>-3.955480376490048</v>
+        <v>-5.035223354783143</v>
       </c>
       <c r="G72">
-        <v>-6.958119007290672</v>
+        <v>-15.80659478283779</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>0.03548222097983231</v>
       </c>
       <c r="E73">
-        <v>-16.90787038119225</v>
+        <v>-27.41106808341464</v>
       </c>
       <c r="F73">
-        <v>-4.050891531218655</v>
+        <v>-5.23168048988749</v>
       </c>
       <c r="G73">
-        <v>-5.804039658481961</v>
+        <v>-15.48373548439314</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>0.1751733301542086</v>
       </c>
       <c r="E74">
-        <v>-15.97227406578554</v>
+        <v>-28.84794835757443</v>
       </c>
       <c r="F74">
-        <v>-4.035966686671554</v>
+        <v>-5.0567752167334</v>
       </c>
       <c r="G74">
-        <v>-7.148693871804357</v>
+        <v>-15.25524659709095</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>0.3636577566736404</v>
       </c>
       <c r="E75">
-        <v>-15.50458685569536</v>
+        <v>-28.32567945026981</v>
       </c>
       <c r="F75">
-        <v>-4.315950847315051</v>
+        <v>-5.47600038516825</v>
       </c>
       <c r="G75">
-        <v>-5.842349291462408</v>
+        <v>-15.35611891967254</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>0.5976184387812885</v>
       </c>
       <c r="E76">
-        <v>-17.59754338713843</v>
+        <v>-28.21582319931774</v>
       </c>
       <c r="F76">
-        <v>-4.567041877237272</v>
+        <v>-5.550370423104328</v>
       </c>
       <c r="G76">
-        <v>-5.446765583883815</v>
+        <v>-14.4094055223527</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>0.8695034557913449</v>
       </c>
       <c r="E77">
-        <v>-16.38875782027098</v>
+        <v>-29.76322767434574</v>
       </c>
       <c r="F77">
-        <v>-4.421559484433173</v>
+        <v>-4.885404775182571</v>
       </c>
       <c r="G77">
-        <v>-5.279136110502818</v>
+        <v>-15.33434711693353</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>1.175197461710092</v>
       </c>
       <c r="E78">
-        <v>-17.32658667336348</v>
+        <v>-29.35968856281122</v>
       </c>
       <c r="F78">
-        <v>-4.1332743292339</v>
+        <v>-5.697632901357381</v>
       </c>
       <c r="G78">
-        <v>-4.805552639473457</v>
+        <v>-15.05966453244912</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>1.510146877433747</v>
       </c>
       <c r="E79">
-        <v>-17.94883975828346</v>
+        <v>-30.98342725994952</v>
       </c>
       <c r="F79">
-        <v>-4.467565349423731</v>
+        <v>-5.1670589537139</v>
       </c>
       <c r="G79">
-        <v>-6.519163842602087</v>
+        <v>-13.94063889508298</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>1.867404004656632</v>
       </c>
       <c r="E80">
-        <v>-17.60087181553406</v>
+        <v>-29.0876269013784</v>
       </c>
       <c r="F80">
-        <v>-4.539752248755376</v>
+        <v>-5.252708145179738</v>
       </c>
       <c r="G80">
-        <v>-4.814597049886746</v>
+        <v>-13.98732255300501</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>2.239958147484249</v>
       </c>
       <c r="E81">
-        <v>-18.33991877358587</v>
+        <v>-30.35716421129575</v>
       </c>
       <c r="F81">
-        <v>-4.646380792483042</v>
+        <v>-5.846205896255459</v>
       </c>
       <c r="G81">
-        <v>-4.445107062248689</v>
+        <v>-14.08377033147337</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>2.625587355269444</v>
       </c>
       <c r="E82">
-        <v>-19.83836818035395</v>
+        <v>-30.98499864043018</v>
       </c>
       <c r="F82">
-        <v>-4.884419710103168</v>
+        <v>-5.681736453231157</v>
       </c>
       <c r="G82">
-        <v>-5.754722461583438</v>
+        <v>-14.58991963897254</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>3.020614471289647</v>
       </c>
       <c r="E83">
-        <v>-19.53261920077807</v>
+        <v>-33.43394077785322</v>
       </c>
       <c r="F83">
-        <v>-4.803381478410131</v>
+        <v>-5.593894620925393</v>
       </c>
       <c r="G83">
-        <v>-4.155315147923046</v>
+        <v>-14.78052926421439</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>3.416310867385158</v>
       </c>
       <c r="E84">
-        <v>-21.87535730153622</v>
+        <v>-33.48675863444168</v>
       </c>
       <c r="F84">
-        <v>-4.912362617275181</v>
+        <v>-5.338453150853461</v>
       </c>
       <c r="G84">
-        <v>-4.725646001792068</v>
+        <v>-13.51187524483704</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>3.811666886979089</v>
       </c>
       <c r="E85">
-        <v>-21.66117406639543</v>
+        <v>-34.31271380141169</v>
       </c>
       <c r="F85">
-        <v>-4.213336206230068</v>
+        <v>-5.824585934950838</v>
       </c>
       <c r="G85">
-        <v>-4.981753115255627</v>
+        <v>-14.04197965985838</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>4.203093691335359</v>
       </c>
       <c r="E86">
-        <v>-22.67643076807108</v>
+        <v>-33.18285953649793</v>
       </c>
       <c r="F86">
-        <v>-4.962462362057151</v>
+        <v>-5.409448311483738</v>
       </c>
       <c r="G86">
-        <v>-5.533356213008992</v>
+        <v>-13.97961063717128</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>4.581451312507497</v>
       </c>
       <c r="E87">
-        <v>-24.14661796855729</v>
+        <v>-35.58159448259792</v>
       </c>
       <c r="F87">
-        <v>-5.055326917673731</v>
+        <v>-5.897582108005273</v>
       </c>
       <c r="G87">
-        <v>-5.553563782980703</v>
+        <v>-14.32052565098712</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>4.941544587161321</v>
       </c>
       <c r="E88">
-        <v>-24.00460955215075</v>
+        <v>-35.45347036749891</v>
       </c>
       <c r="F88">
-        <v>-4.288840177601601</v>
+        <v>-5.466916248037289</v>
       </c>
       <c r="G88">
-        <v>-4.70365404777469</v>
+        <v>-14.78651638582216</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>5.277553443438915</v>
       </c>
       <c r="E89">
-        <v>-26.58590313515896</v>
+        <v>-36.56154720090977</v>
       </c>
       <c r="F89">
-        <v>-4.586920553887867</v>
+        <v>-5.820672597633787</v>
       </c>
       <c r="G89">
-        <v>-4.37582727574836</v>
+        <v>-13.44427556019789</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>5.579132397203225</v>
       </c>
       <c r="E90">
-        <v>-26.8670036307111</v>
+        <v>-37.26894238988496</v>
       </c>
       <c r="F90">
-        <v>-5.102544317689601</v>
+        <v>-6.20372909037183</v>
       </c>
       <c r="G90">
-        <v>-4.30433273428226</v>
+        <v>-14.73867238168861</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>5.8352109820954</v>
       </c>
       <c r="E91">
-        <v>-28.59378775389393</v>
+        <v>-37.50110819531021</v>
       </c>
       <c r="F91">
-        <v>-5.166647190175885</v>
+        <v>-6.246262680142787</v>
       </c>
       <c r="G91">
-        <v>-4.85918347720965</v>
+        <v>-13.23974674623618</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>6.03853283112006</v>
       </c>
       <c r="E92">
-        <v>-29.94342924053296</v>
+        <v>-39.29542545136943</v>
       </c>
       <c r="F92">
-        <v>-4.748463308380438</v>
+        <v>-5.730680884547813</v>
       </c>
       <c r="G92">
-        <v>-3.883340589689761</v>
+        <v>-14.09326001026169</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>6.17816953455451</v>
       </c>
       <c r="E93">
-        <v>-32.61838298720482</v>
+        <v>-41.67586309824144</v>
       </c>
       <c r="F93">
-        <v>-4.996574595622758</v>
+        <v>-6.322680845754008</v>
       </c>
       <c r="G93">
-        <v>-5.241991789552196</v>
+        <v>-15.19482914099925</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>6.239782711976662</v>
       </c>
       <c r="E94">
-        <v>-33.84192005815225</v>
+        <v>-41.91999086775794</v>
       </c>
       <c r="F94">
-        <v>-5.144890238309578</v>
+        <v>-5.878328995191276</v>
       </c>
       <c r="G94">
-        <v>-5.003284903443046</v>
+        <v>-14.54779625753085</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>6.220015160650043</v>
       </c>
       <c r="E95">
-        <v>-36.13644349615073</v>
+        <v>-41.72805376117984</v>
       </c>
       <c r="F95">
-        <v>-5.49321051735133</v>
+        <v>-6.335605469729909</v>
       </c>
       <c r="G95">
-        <v>-5.625975345561182</v>
+        <v>-13.41184214554965</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>6.106716112156794</v>
       </c>
       <c r="E96">
-        <v>-37.86227663979196</v>
+        <v>-47.10514115551758</v>
       </c>
       <c r="F96">
-        <v>-5.465275528708894</v>
+        <v>-6.044839043287621</v>
       </c>
       <c r="G96">
-        <v>-6.675004463317739</v>
+        <v>-14.26057994763476</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>5.899884836104569</v>
       </c>
       <c r="E97">
-        <v>-39.66376473444233</v>
+        <v>-47.28492157362209</v>
       </c>
       <c r="F97">
-        <v>-5.116921991842918</v>
+        <v>-6.26269758828026</v>
       </c>
       <c r="G97">
-        <v>-5.298019462258821</v>
+        <v>-14.30804158375853</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>5.586113975485418</v>
       </c>
       <c r="E98">
-        <v>-42.2044741333938</v>
+        <v>-48.8308497661236</v>
       </c>
       <c r="F98">
-        <v>-5.475522897834745</v>
+        <v>-6.009773418760918</v>
       </c>
       <c r="G98">
-        <v>-6.293053582269866</v>
+        <v>-15.40362855870662</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>5.19247160381416</v>
       </c>
       <c r="E99">
-        <v>-43.770295912211</v>
+        <v>-49.23542816244287</v>
       </c>
       <c r="F99">
-        <v>-5.187198149987585</v>
+        <v>-5.847340621543871</v>
       </c>
       <c r="G99">
-        <v>-6.239694209267892</v>
+        <v>-15.37512145106796</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>4.686859419355311</v>
       </c>
       <c r="E100">
-        <v>-46.55286205096412</v>
+        <v>-51.25593703459273</v>
       </c>
       <c r="F100">
-        <v>-5.257877361287733</v>
+        <v>-6.399397539930289</v>
       </c>
       <c r="G100">
-        <v>-6.242842538075739</v>
+        <v>-14.66671436384701</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>4.136142347700368</v>
       </c>
       <c r="E101">
-        <v>-48.11266548782513</v>
+        <v>-52.83394380484606</v>
       </c>
       <c r="F101">
-        <v>-5.438289179909805</v>
+        <v>-6.158848052507713</v>
       </c>
       <c r="G101">
-        <v>-6.872034891633003</v>
+        <v>-15.5874002521371</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>3.460331438076271</v>
       </c>
       <c r="E102">
-        <v>-50.65587120807333</v>
+        <v>-54.52116151850538</v>
       </c>
       <c r="F102">
-        <v>-5.537060166738017</v>
+        <v>-6.16000890894373</v>
       </c>
       <c r="G102">
-        <v>-8.325149197913001</v>
+        <v>-14.87840057726463</v>
       </c>
     </row>
   </sheetData>
